--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_prop_cas.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.148</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.2173</v>
+        <v>-0.285</v>
       </c>
       <c r="G2">
-        <v>0.04371380612673101</v>
+        <v>-0.04250350303596449</v>
       </c>
       <c r="H2">
-        <v>0.04371380612673101</v>
+        <v>-0.04250350303596449</v>
       </c>
       <c r="I2">
-        <v>-0.02339488040285354</v>
+        <v>-0.0646893974778141</v>
       </c>
       <c r="J2">
-        <v>-0.01975307735347601</v>
+        <v>-0.05923014154427199</v>
       </c>
       <c r="K2">
-        <v>-30.82</v>
+        <v>-54.27</v>
       </c>
       <c r="L2">
-        <v>-0.06466638690725976</v>
+        <v>-0.08449322746380195</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>260.96</v>
+        <v>141.4</v>
       </c>
       <c r="V2">
-        <v>0.192689950527948</v>
+        <v>0.1917808219178082</v>
       </c>
       <c r="W2">
-        <v>-0.07838328792007267</v>
+        <v>-0.163023679417122</v>
       </c>
       <c r="X2">
-        <v>0.05353544199961965</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="Y2">
-        <v>-0.1319187299196923</v>
+        <v>-0.2512265945708307</v>
       </c>
       <c r="Z2">
-        <v>1.77220838136318</v>
+        <v>2.668655451361335</v>
       </c>
       <c r="AA2">
-        <v>-0.09974424552429668</v>
+        <v>-0.1726457399103139</v>
       </c>
       <c r="AB2">
-        <v>0.05353544199961965</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="AC2">
-        <v>-0.1532796875239164</v>
+        <v>-0.2608486550640225</v>
       </c>
       <c r="AD2">
-        <v>2.143</v>
+        <v>2.086</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.143</v>
+        <v>2.086</v>
       </c>
       <c r="AG2">
-        <v>-258.817</v>
+        <v>-139.314</v>
       </c>
       <c r="AH2">
-        <v>0.001579867344223089</v>
+        <v>0.002821259802051973</v>
       </c>
       <c r="AI2">
-        <v>0.004005285556487983</v>
+        <v>0.003329151944026837</v>
       </c>
       <c r="AJ2">
-        <v>-0.2362583444927945</v>
+        <v>-0.232972009378146</v>
       </c>
       <c r="AK2">
-        <v>-0.944301543692969</v>
+        <v>-0.2871352429789812</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0.2616605616605617</v>
+        <v>-0.05490918662806001</v>
       </c>
       <c r="AP2">
-        <v>31.6015873015873</v>
+        <v>3.667122927086075</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Buruj Cooperative Insurance Company (SASE:8270)</t>
+          <t>Arabian Shield Cooperative Insurance Company (SASE:8070)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,28 +713,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.148</v>
+        <v>0.0154</v>
       </c>
       <c r="E3">
-        <v>-0.341</v>
+        <v>-0.285</v>
       </c>
       <c r="G3">
-        <v>0.09842519685039371</v>
+        <v>0.06420851875397329</v>
       </c>
       <c r="H3">
-        <v>0.09842519685039371</v>
+        <v>0.06420851875397329</v>
       </c>
       <c r="I3">
-        <v>0.09311023622047246</v>
+        <v>0.05905912269548632</v>
       </c>
       <c r="J3">
-        <v>0.04655511811023623</v>
+        <v>0.03413858868404322</v>
       </c>
       <c r="K3">
-        <v>1.72</v>
+        <v>5.37</v>
       </c>
       <c r="L3">
-        <v>0.03385826771653543</v>
+        <v>0.03413858868404323</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>53</v>
+        <v>14.7</v>
       </c>
       <c r="V3">
-        <v>0.3001132502831257</v>
+        <v>0.05509745127436282</v>
       </c>
       <c r="W3">
-        <v>0.01512752858399296</v>
+        <v>0.04096109839816934</v>
       </c>
       <c r="X3">
-        <v>0.05367525472861486</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="Y3">
-        <v>-0.0385477261446219</v>
+        <v>-0.04724181675553932</v>
       </c>
       <c r="Z3">
-        <v>0.6909684439608269</v>
+        <v>8.025510204081636</v>
       </c>
       <c r="AA3">
-        <v>0.03216811751904244</v>
+        <v>0.2739795918367348</v>
       </c>
       <c r="AB3">
-        <v>0.05353851865324705</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="AC3">
-        <v>-0.02137040113420461</v>
+        <v>0.1857766766830261</v>
       </c>
       <c r="AD3">
-        <v>0.803</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.803</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-52.197</v>
+        <v>-14.7</v>
       </c>
       <c r="AH3">
-        <v>0.004526417253372265</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.00668592791187564</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.4195799136676769</v>
+        <v>-0.05831019436731455</v>
       </c>
       <c r="AK3">
-        <v>-0.7778638808995127</v>
+        <v>-0.05265042979942693</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.1565302144249513</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-10.17485380116959</v>
+        <v>-1.495422177009156</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Alamiya for Cooperative Insurance Company (SASE:8280)</t>
+          <t>Buruj Cooperative Insurance Company (SASE:8270)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,25 +838,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.172</v>
+        <v>-0.0508</v>
       </c>
       <c r="G4">
-        <v>0.03256916996047431</v>
+        <v>0.04522167487684729</v>
       </c>
       <c r="H4">
-        <v>0.03256916996047431</v>
+        <v>0.04522167487684729</v>
       </c>
       <c r="I4">
-        <v>-0.2640316205533597</v>
+        <v>-0.05852216748768473</v>
       </c>
       <c r="J4">
-        <v>-0.2640316205533597</v>
+        <v>-0.05852216748768473</v>
       </c>
       <c r="K4">
-        <v>-8.630000000000001</v>
+        <v>-8.74</v>
       </c>
       <c r="L4">
-        <v>-0.341106719367589</v>
+        <v>-0.08610837438423645</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>12.2</v>
+        <v>19.8</v>
       </c>
       <c r="V4">
-        <v>0.05014385532264693</v>
+        <v>0.1575178997613365</v>
       </c>
       <c r="W4">
-        <v>-0.07838328792007267</v>
+        <v>-0.0732606873428332</v>
       </c>
       <c r="X4">
-        <v>0.05353544199961965</v>
+        <v>0.08834000136536829</v>
       </c>
       <c r="Y4">
-        <v>-0.1319187299196923</v>
+        <v>-0.1616006887082015</v>
       </c>
       <c r="Z4">
-        <v>0.2379608728367194</v>
+        <v>1.51260003278542</v>
       </c>
       <c r="AA4">
-        <v>-0.06282919488337095</v>
+        <v>-0.08852063246054574</v>
       </c>
       <c r="AB4">
-        <v>0.05353544199961965</v>
+        <v>0.08818930370097985</v>
       </c>
       <c r="AC4">
-        <v>-0.1163646368829906</v>
+        <v>-0.1767099361615256</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AG4">
-        <v>-12.2</v>
+        <v>-19.364</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.00345658654151075</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.004194889162561576</v>
       </c>
       <c r="AJ4">
-        <v>-0.05279099956728688</v>
+        <v>-0.1821020162503762</v>
       </c>
       <c r="AK4">
-        <v>-0.1367713004484305</v>
+        <v>-0.2301511837976609</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>-0.07898550724637682</v>
       </c>
       <c r="AP4">
-        <v>2.029950083194676</v>
+        <v>3.507971014492754</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Malath Cooperative Insurance Company (SASE:8020)</t>
+          <t>Al Alamiya for Cooperative Insurance Company (SASE:8280)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.145</v>
+        <v>0.0357</v>
       </c>
       <c r="G5">
-        <v>0.02910990009082652</v>
+        <v>-0.1162257495590829</v>
       </c>
       <c r="H5">
-        <v>0.02910990009082652</v>
+        <v>-0.1162257495590829</v>
       </c>
       <c r="I5">
-        <v>-0.03542234332425068</v>
+        <v>-0.2716049382716049</v>
       </c>
       <c r="J5">
-        <v>-0.03542234332425068</v>
+        <v>-0.2716049382716049</v>
       </c>
       <c r="K5">
-        <v>-11.8</v>
+        <v>-16.9</v>
       </c>
       <c r="L5">
-        <v>-0.05358764759309719</v>
+        <v>-0.2980599647266314</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,31 +1002,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>94.59999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="V5">
-        <v>0.3121082151105246</v>
+        <v>0.08408903544929926</v>
       </c>
       <c r="W5">
-        <v>-0.09624796084828713</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="X5">
-        <v>0.05353544199961965</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="Y5">
-        <v>-0.1497834028479068</v>
+        <v>-0.2548695818203753</v>
       </c>
       <c r="Z5">
-        <v>2.815856777493607</v>
+        <v>0.6356502242152466</v>
       </c>
       <c r="AA5">
-        <v>-0.09974424552429668</v>
+        <v>-0.1726457399103139</v>
       </c>
       <c r="AB5">
-        <v>0.05353544199961965</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="AC5">
-        <v>-0.1532796875239164</v>
+        <v>-0.2608486550640225</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-94.59999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.4537170263788968</v>
+        <v>-0.0918091809180918</v>
       </c>
       <c r="AK5">
-        <v>-6.223684210526314</v>
+        <v>-0.1410788381742739</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>-0</v>
       </c>
       <c r="AP5">
-        <v>12.76653171390013</v>
+        <v>0.7083333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arabian Shield Cooperative Insurance Company (SASE:8070)</t>
+          <t>United Cooperative Assurance Company (SASE:8190)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,28 +1082,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00365</v>
-      </c>
-      <c r="E6">
-        <v>-0.09359999999999999</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="G6">
-        <v>0.1076512455516014</v>
+        <v>-0.2216216216216216</v>
       </c>
       <c r="H6">
-        <v>0.1076512455516014</v>
+        <v>-0.2216216216216216</v>
       </c>
       <c r="I6">
-        <v>0.1067615658362989</v>
+        <v>-0.1986486486486486</v>
       </c>
       <c r="J6">
-        <v>0.07704626334519572</v>
+        <v>-0.1986486486486486</v>
       </c>
       <c r="K6">
-        <v>8.69</v>
+        <v>-16.1</v>
       </c>
       <c r="L6">
-        <v>0.07731316725978647</v>
+        <v>-0.2175675675675676</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,7 +1109,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1121,61 +1118,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>99</v>
+        <v>15.4</v>
       </c>
       <c r="V6">
-        <v>0.3672106824925816</v>
+        <v>0.2010443864229765</v>
       </c>
       <c r="W6">
-        <v>0.071405094494659</v>
+        <v>-0.2258064516129032</v>
       </c>
       <c r="X6">
-        <v>0.05353544199961965</v>
+        <v>0.08905424476210155</v>
       </c>
       <c r="Y6">
-        <v>0.01786965249503934</v>
+        <v>-0.3148606963750048</v>
       </c>
       <c r="Z6">
-        <v>-4.323076923076925</v>
+        <v>1.492537313432836</v>
       </c>
       <c r="AA6">
-        <v>-0.3330769230769233</v>
+        <v>-0.2964905203711173</v>
       </c>
       <c r="AB6">
-        <v>0.05353544199961965</v>
+        <v>0.08824977239695057</v>
       </c>
       <c r="AC6">
-        <v>-0.386612365076543</v>
+        <v>-0.3847402927680679</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>-99</v>
+        <v>-13.75</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.02108626198083067</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.02933333333333333</v>
       </c>
       <c r="AJ6">
-        <v>-0.5803048065650644</v>
+        <v>-0.2187748607796341</v>
       </c>
       <c r="AK6">
-        <v>-3.084112149532711</v>
+        <v>-0.3365973072215422</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1184,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>-0.1213235294117647</v>
       </c>
       <c r="AP6">
-        <v>-7.92</v>
+        <v>1.011029411764706</v>
       </c>
     </row>
     <row r="7">
@@ -1198,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Cooperative Assurance Company (SASE:8190)</t>
+          <t>Malath Cooperative Insurance Company (SASE:8020)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1207,25 +1204,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.207</v>
+        <v>-0.0565</v>
       </c>
       <c r="G7">
-        <v>-0.05154639175257732</v>
+        <v>-0.07515822784810126</v>
       </c>
       <c r="H7">
-        <v>-0.05154639175257732</v>
+        <v>-0.07515822784810126</v>
       </c>
       <c r="I7">
-        <v>-0.1973490427098674</v>
+        <v>-0.05854430379746835</v>
       </c>
       <c r="J7">
-        <v>-0.1973490427098674</v>
+        <v>-0.05854430379746835</v>
       </c>
       <c r="K7">
-        <v>-20.8</v>
+        <v>-17.9</v>
       </c>
       <c r="L7">
-        <v>-0.3063328424153166</v>
+        <v>-0.07080696202531644</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1249,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>81.3</v>
       </c>
       <c r="V7">
-        <v>0.005971799834116671</v>
+        <v>0.5534377127297481</v>
       </c>
       <c r="W7">
-        <v>-0.219409282700422</v>
+        <v>-0.163023679417122</v>
       </c>
       <c r="X7">
-        <v>0.05364935627615709</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="Y7">
-        <v>-0.2730586389765791</v>
+        <v>-0.2512265945708307</v>
       </c>
       <c r="Z7">
-        <v>1.840607210626186</v>
+        <v>16.63157894736842</v>
       </c>
       <c r="AA7">
-        <v>-0.3632420710219573</v>
+        <v>-0.9736842105263157</v>
       </c>
       <c r="AB7">
-        <v>0.05353795084756123</v>
+        <v>0.08820291515370866</v>
       </c>
       <c r="AC7">
-        <v>-0.4167800218695185</v>
+        <v>-1.061887125680024</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.8200000000000001</v>
+        <v>-81.3</v>
       </c>
       <c r="AH7">
-        <v>0.00369105332745703</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.01844713656387665</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.00227222345377965</v>
+        <v>-1.239329268292683</v>
       </c>
       <c r="AK7">
-        <v>-0.01163450624290579</v>
+        <v>-9.344827586206893</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1306,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-0.1080645161290323</v>
+        <v>-0</v>
       </c>
       <c r="AP7">
-        <v>0.06612903225806452</v>
+        <v>5.685314685314685</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.03700000000000001</v>
+        <v>0.13275</v>
       </c>
       <c r="E2">
-        <v>-0.285</v>
+        <v>-0.27</v>
       </c>
       <c r="G2">
-        <v>-0.04250350303596449</v>
+        <v>-0.04844787644787645</v>
       </c>
       <c r="H2">
-        <v>-0.04250350303596449</v>
+        <v>-0.04844787644787645</v>
       </c>
       <c r="I2">
-        <v>-0.0646893974778141</v>
+        <v>0.04261003861003861</v>
       </c>
       <c r="J2">
-        <v>-0.05923014154427199</v>
+        <v>0.02668813740904684</v>
       </c>
       <c r="K2">
-        <v>-54.27</v>
+        <v>20.068</v>
       </c>
       <c r="L2">
-        <v>-0.08449322746380195</v>
+        <v>0.0309930501930502</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,73 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>141.4</v>
+        <v>127</v>
       </c>
       <c r="V2">
-        <v>0.1917808219178082</v>
+        <v>0.1869571617841896</v>
       </c>
       <c r="W2">
-        <v>-0.163023679417122</v>
+        <v>0.02786824769433465</v>
       </c>
       <c r="X2">
-        <v>0.08820291515370866</v>
+        <v>0.07599931898917334</v>
       </c>
       <c r="Y2">
-        <v>-0.2512265945708307</v>
+        <v>-0.04813107129483869</v>
       </c>
       <c r="Z2">
-        <v>2.668655451361335</v>
+        <v>3.498373728969236</v>
       </c>
       <c r="AA2">
-        <v>-0.1726457399103139</v>
+        <v>0.04113653178250745</v>
       </c>
       <c r="AB2">
-        <v>0.08820291515370866</v>
+        <v>0.07598562759967514</v>
       </c>
       <c r="AC2">
-        <v>-0.2608486550640225</v>
+        <v>-0.03485266669658871</v>
       </c>
       <c r="AD2">
-        <v>2.086</v>
+        <v>1.277</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.086</v>
+        <v>1.277</v>
       </c>
       <c r="AG2">
-        <v>-139.314</v>
+        <v>-125.723</v>
       </c>
       <c r="AH2">
-        <v>0.002821259802051973</v>
+        <v>0.001876349039124155</v>
       </c>
       <c r="AI2">
-        <v>0.003329151944026837</v>
+        <v>0.003305917774032624</v>
       </c>
       <c r="AJ2">
-        <v>-0.232972009378146</v>
+        <v>-0.2271102303744556</v>
       </c>
       <c r="AK2">
-        <v>-0.2871352429789812</v>
+        <v>-0.4848983905244199</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>5.271</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>4.877</v>
       </c>
       <c r="AN2">
-        <v>-0.05490918662806001</v>
+        <v>0.04236894492368944</v>
+      </c>
+      <c r="AO2">
+        <v>5.23430089167141</v>
       </c>
       <c r="AP2">
-        <v>3.667122927086075</v>
+        <v>-4.171300597213006</v>
+      </c>
+      <c r="AQ2">
+        <v>5.657166290752512</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arabian Shield Cooperative Insurance Company (SASE:8070)</t>
+          <t>Malath Cooperative Insurance Company (SASE:8020)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,28 +719,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0154</v>
-      </c>
-      <c r="E3">
-        <v>-0.285</v>
+        <v>0.0765</v>
       </c>
       <c r="G3">
-        <v>0.06420851875397329</v>
+        <v>-0.01192368839427663</v>
       </c>
       <c r="H3">
-        <v>0.06420851875397329</v>
+        <v>-0.01192368839427663</v>
       </c>
       <c r="I3">
-        <v>0.05905912269548632</v>
+        <v>0.07034976152623211</v>
       </c>
       <c r="J3">
-        <v>0.03413858868404322</v>
+        <v>0.0614361269692152</v>
       </c>
       <c r="K3">
-        <v>5.37</v>
+        <v>15.4</v>
       </c>
       <c r="L3">
-        <v>0.03413858868404323</v>
+        <v>0.06120826709062004</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,31 +761,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.7</v>
+        <v>37.2</v>
       </c>
       <c r="V3">
-        <v>0.05509745127436282</v>
+        <v>0.1585002130379208</v>
       </c>
       <c r="W3">
-        <v>0.04096109839816934</v>
+        <v>0.1711111111111111</v>
       </c>
       <c r="X3">
-        <v>0.08820291515370866</v>
+        <v>0.07598562759967514</v>
       </c>
       <c r="Y3">
-        <v>-0.04724181675553932</v>
+        <v>0.09512548351143596</v>
       </c>
       <c r="Z3">
-        <v>8.025510204081636</v>
+        <v>28.91954022988505</v>
       </c>
       <c r="AA3">
-        <v>0.2739795918367348</v>
+        <v>1.776704545454545</v>
       </c>
       <c r="AB3">
-        <v>0.08820291515370866</v>
+        <v>0.07598562759967514</v>
       </c>
       <c r="AC3">
-        <v>0.1857766766830261</v>
+        <v>1.70071891785487</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-14.7</v>
+        <v>-37.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,22 +806,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.05831019436731455</v>
+        <v>-0.1883544303797469</v>
       </c>
       <c r="AK3">
-        <v>-0.05265042979942693</v>
+        <v>-0.5731895223420649</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>5.619047619047619</v>
+      </c>
       <c r="AP3">
-        <v>-1.495422177009156</v>
+        <v>-2.05524861878453</v>
+      </c>
+      <c r="AQ3">
+        <v>5.619047619047619</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Buruj Cooperative Insurance Company (SASE:8270)</t>
+          <t>United Cooperative Assurance Company (SASE:8190)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,25 +847,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0508</v>
+        <v>0.28</v>
       </c>
       <c r="G4">
-        <v>0.04522167487684729</v>
+        <v>-0.0528658875904285</v>
       </c>
       <c r="H4">
-        <v>0.04522167487684729</v>
+        <v>-0.0528658875904285</v>
       </c>
       <c r="I4">
-        <v>-0.05852216748768473</v>
+        <v>0.009181969949916527</v>
       </c>
       <c r="J4">
-        <v>-0.05852216748768473</v>
+        <v>0.004590984974958264</v>
       </c>
       <c r="K4">
-        <v>-8.74</v>
+        <v>-0.332</v>
       </c>
       <c r="L4">
-        <v>-0.08610837438423645</v>
+        <v>-0.001847523650528659</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,67 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>19.8</v>
+        <v>32.2</v>
       </c>
       <c r="V4">
-        <v>0.1575178997613365</v>
+        <v>0.3473570658036678</v>
       </c>
       <c r="W4">
-        <v>-0.0732606873428332</v>
+        <v>-0.006080586080586081</v>
       </c>
       <c r="X4">
-        <v>0.08834000136536829</v>
+        <v>0.07634825766817682</v>
       </c>
       <c r="Y4">
-        <v>-0.1616006887082015</v>
+        <v>-0.0824288437487629</v>
       </c>
       <c r="Z4">
-        <v>1.51260003278542</v>
+        <v>9.00751879699248</v>
       </c>
       <c r="AA4">
-        <v>-0.08852063246054574</v>
+        <v>0.04135338345864661</v>
       </c>
       <c r="AB4">
-        <v>0.08818930370097985</v>
+        <v>0.07599276935851718</v>
       </c>
       <c r="AC4">
-        <v>-0.1767099361615256</v>
+        <v>-0.03463938589987057</v>
       </c>
       <c r="AD4">
-        <v>0.436</v>
+        <v>1.13</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.436</v>
+        <v>1.13</v>
       </c>
       <c r="AG4">
-        <v>-19.364</v>
+        <v>-31.07</v>
       </c>
       <c r="AH4">
-        <v>0.00345658654151075</v>
+        <v>0.01204305659170841</v>
       </c>
       <c r="AI4">
-        <v>0.004194889162561576</v>
+        <v>0.01688331092185866</v>
       </c>
       <c r="AJ4">
-        <v>-0.1821020162503762</v>
+        <v>-0.5041375953269512</v>
       </c>
       <c r="AK4">
-        <v>-0.2301511837976609</v>
+        <v>-0.8946156061042331</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.991</v>
       </c>
       <c r="AN4">
-        <v>-0.07898550724637682</v>
+        <v>0.4064748201438849</v>
+      </c>
+      <c r="AO4">
+        <v>1.664984863773966</v>
       </c>
       <c r="AP4">
-        <v>3.507971014492754</v>
+        <v>-11.17625899280576</v>
+      </c>
+      <c r="AQ4">
+        <v>1.664984863773966</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Alamiya for Cooperative Insurance Company (SASE:8280)</t>
+          <t>Liva Insurance Company (SASE:8280)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,25 +975,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0357</v>
+        <v>0.189</v>
+      </c>
+      <c r="E5">
+        <v>-0.173</v>
       </c>
       <c r="G5">
-        <v>-0.1162257495590829</v>
+        <v>-0.0941385435168739</v>
       </c>
       <c r="H5">
-        <v>-0.1162257495590829</v>
+        <v>-0.0941385435168739</v>
       </c>
       <c r="I5">
-        <v>-0.2716049382716049</v>
+        <v>0.04271758436944938</v>
       </c>
       <c r="J5">
-        <v>-0.2716049382716049</v>
+        <v>0.02627435942886703</v>
       </c>
       <c r="K5">
-        <v>-16.9</v>
+        <v>3.02</v>
       </c>
       <c r="L5">
-        <v>-0.2980599647266314</v>
+        <v>0.02682060390763766</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -987,7 +1005,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -996,37 +1014,37 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>10.2</v>
+        <v>25.6</v>
       </c>
       <c r="V5">
-        <v>0.08408903544929926</v>
+        <v>0.1331945889698231</v>
       </c>
       <c r="W5">
-        <v>-0.1666666666666666</v>
+        <v>0.03660606060606061</v>
       </c>
       <c r="X5">
-        <v>0.08820291515370866</v>
+        <v>0.07598562759967514</v>
       </c>
       <c r="Y5">
-        <v>-0.2548695818203753</v>
+        <v>-0.03937956699361454</v>
       </c>
       <c r="Z5">
-        <v>0.6356502242152466</v>
+        <v>1.557399723374827</v>
       </c>
       <c r="AA5">
-        <v>-0.1726457399103139</v>
+        <v>0.0409196801063683</v>
       </c>
       <c r="AB5">
-        <v>0.08820291515370866</v>
+        <v>0.07598562759967514</v>
       </c>
       <c r="AC5">
-        <v>-0.2608486550640225</v>
+        <v>-0.03506594749330685</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1038,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-10.2</v>
+        <v>-25.6</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1047,22 +1065,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.0918091809180918</v>
+        <v>-0.1536614645858344</v>
       </c>
       <c r="AK5">
-        <v>-0.1410788381742739</v>
+        <v>-0.3381770145310437</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>4.256637168141593</v>
       </c>
       <c r="AP5">
-        <v>0.7083333333333333</v>
+        <v>-4.714548802946593</v>
+      </c>
+      <c r="AQ5">
+        <v>4.256637168141593</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Cooperative Assurance Company (SASE:8190)</t>
+          <t>Buruj Cooperative Insurance Company (SASE:8270)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,25 +1106,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.03700000000000001</v>
+        <v>-0.0144</v>
+      </c>
+      <c r="E6">
+        <v>-0.367</v>
       </c>
       <c r="G6">
-        <v>-0.2216216216216216</v>
+        <v>-0.07982625482625483</v>
       </c>
       <c r="H6">
-        <v>-0.2216216216216216</v>
+        <v>-0.07982625482625483</v>
       </c>
       <c r="I6">
-        <v>-0.1986486486486486</v>
+        <v>0.03310810810810811</v>
       </c>
       <c r="J6">
-        <v>-0.1986486486486486</v>
+        <v>0.01711594100628043</v>
       </c>
       <c r="K6">
-        <v>-16.1</v>
+        <v>1.98</v>
       </c>
       <c r="L6">
-        <v>-0.2175675675675676</v>
+        <v>0.01911196911196911</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1109,7 +1136,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1118,195 +1145,76 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>15.4</v>
+        <v>32</v>
       </c>
       <c r="V6">
-        <v>0.2010443864229765</v>
+        <v>0.200375704445836</v>
       </c>
       <c r="W6">
-        <v>-0.2258064516129032</v>
+        <v>0.01913043478260869</v>
       </c>
       <c r="X6">
-        <v>0.08905424476210155</v>
+        <v>0.07601301037867153</v>
       </c>
       <c r="Y6">
-        <v>-0.3148606963750048</v>
+        <v>-0.05688257559606284</v>
       </c>
       <c r="Z6">
-        <v>1.492537313432836</v>
+        <v>1.231339735666064</v>
       </c>
       <c r="AA6">
-        <v>-0.2964905203711173</v>
+        <v>0.02107553827434929</v>
       </c>
       <c r="AB6">
-        <v>0.08824977239695057</v>
+        <v>0.0759818970483483</v>
       </c>
       <c r="AC6">
-        <v>-0.3847402927680679</v>
+        <v>-0.05490635877399901</v>
       </c>
       <c r="AD6">
-        <v>1.65</v>
+        <v>0.147</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>0.147</v>
       </c>
       <c r="AG6">
-        <v>-13.75</v>
+        <v>-31.853</v>
       </c>
       <c r="AH6">
-        <v>0.02108626198083067</v>
+        <v>0.0009196293956095517</v>
       </c>
       <c r="AI6">
-        <v>0.02933333333333333</v>
+        <v>0.001267820642189966</v>
       </c>
       <c r="AJ6">
-        <v>-0.2187748607796341</v>
+        <v>-0.2491493738609432</v>
       </c>
       <c r="AK6">
-        <v>-0.3365973072215422</v>
+        <v>-0.3794417906536267</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-0.394</v>
       </c>
       <c r="AN6">
-        <v>-0.1213235294117647</v>
+        <v>0.03838120104438642</v>
       </c>
       <c r="AP6">
-        <v>1.011029411764706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Malath Cooperative Insurance Company (SASE:8020)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.0565</v>
-      </c>
-      <c r="G7">
-        <v>-0.07515822784810126</v>
-      </c>
-      <c r="H7">
-        <v>-0.07515822784810126</v>
-      </c>
-      <c r="I7">
-        <v>-0.05854430379746835</v>
-      </c>
-      <c r="J7">
-        <v>-0.05854430379746835</v>
-      </c>
-      <c r="K7">
-        <v>-17.9</v>
-      </c>
-      <c r="L7">
-        <v>-0.07080696202531644</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>81.3</v>
-      </c>
-      <c r="V7">
-        <v>0.5534377127297481</v>
-      </c>
-      <c r="W7">
-        <v>-0.163023679417122</v>
-      </c>
-      <c r="X7">
-        <v>0.08820291515370866</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2512265945708307</v>
-      </c>
-      <c r="Z7">
-        <v>16.63157894736842</v>
-      </c>
-      <c r="AA7">
-        <v>-0.9736842105263157</v>
-      </c>
-      <c r="AB7">
-        <v>0.08820291515370866</v>
-      </c>
-      <c r="AC7">
-        <v>-1.061887125680024</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>-81.3</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>-1.239329268292683</v>
-      </c>
-      <c r="AK7">
-        <v>-9.344827586206893</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AP7">
-        <v>5.685314685314685</v>
+        <v>-8.316710182767624</v>
+      </c>
+      <c r="AQ6">
+        <v>-8.705583756345177</v>
       </c>
     </row>
   </sheetData>
